--- a/AEO.xlsx
+++ b/AEO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82688C77-40A3-47E3-A5D7-1A71A7C951BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394E8180-DBEB-41BD-B317-43022EBDA47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{3AF04D28-8998-4CB9-8994-9DFD7A9E4F0F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{3AF04D28-8998-4CB9-8994-9DFD7A9E4F0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>American Eagle Outfiters</t>
   </si>
@@ -182,13 +182,45 @@
   <si>
     <t>Brands:</t>
   </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Minority Interest</t>
+  </si>
+  <si>
+    <t>Net Income to Shareholders</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -205,16 +237,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -260,29 +290,38 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -636,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>14.35</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -644,10 +683,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>192.10178300000001</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>10</v>
+        <v>167.57333299999999</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -659,21 +698,21 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>2756.6605860499999</v>
+        <v>2910.7487942100001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>160.19499999999999</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>10</v>
+        <v>103.286</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -681,10 +720,10 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>10</v>
+        <v>85</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -693,7 +732,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>2596.4655860499997</v>
+        <v>2892.4627942100001</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -715,13 +754,16 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{E6F8A4DF-B7EA-48D7-BCDA-EC12510E4C1F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B74C3300-CB92-4F6E-827D-008A8029E743}">
-  <dimension ref="A1:AZ284"/>
+  <dimension ref="A1:BU286"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -729,12 +771,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:73" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -759,8 +801,32 @@
       <c r="J2" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="K2" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
@@ -776,11 +842,15 @@
         <v>1186</v>
       </c>
       <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="K3" s="8">
+        <v>1176</v>
+      </c>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
+      <c r="O3" s="8">
+        <v>1170</v>
+      </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -797,7 +867,7 @@
       <c r="AC3" s="8"/>
       <c r="AD3" s="8"/>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
@@ -813,11 +883,15 @@
         <v>7282</v>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+      <c r="K4" s="8">
+        <v>7232</v>
+      </c>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
+      <c r="O4" s="8">
+        <v>7220</v>
+      </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -834,7 +908,7 @@
       <c r="AC4" s="8"/>
       <c r="AD4" s="8"/>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:73" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -844,1057 +918,1520 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16">
         <v>857.37800000000004</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3">
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16">
         <v>831.91399999999999</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-      <c r="AO6" s="3"/>
-      <c r="AP6" s="3"/>
-      <c r="AQ6" s="3"/>
-      <c r="AR6" s="3"/>
-      <c r="AS6" s="3"/>
-      <c r="AT6" s="3"/>
-      <c r="AU6" s="3"/>
-      <c r="AV6" s="3"/>
-      <c r="AW6" s="3"/>
-      <c r="AX6" s="3"/>
-      <c r="AY6" s="3"/>
-    </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J6" s="16"/>
+      <c r="K6" s="16">
+        <v>693.86500000000001</v>
+      </c>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16">
+        <v>678.476</v>
+      </c>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="16"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="16"/>
+      <c r="AM6" s="16"/>
+      <c r="AN6" s="16"/>
+      <c r="AO6" s="16"/>
+      <c r="AP6" s="16"/>
+      <c r="AQ6" s="16"/>
+      <c r="AR6" s="16"/>
+      <c r="AS6" s="16"/>
+      <c r="AT6" s="16"/>
+      <c r="AU6" s="16"/>
+      <c r="AV6" s="16"/>
+      <c r="AW6" s="16"/>
+      <c r="AX6" s="16"/>
+      <c r="AY6" s="16"/>
+      <c r="AZ6" s="16"/>
+      <c r="BA6" s="16"/>
+      <c r="BB6" s="16"/>
+      <c r="BC6" s="16"/>
+      <c r="BD6" s="16"/>
+      <c r="BE6" s="16"/>
+      <c r="BF6" s="16"/>
+      <c r="BG6" s="16"/>
+      <c r="BH6" s="16"/>
+      <c r="BI6" s="16"/>
+      <c r="BJ6" s="16"/>
+      <c r="BK6" s="16"/>
+      <c r="BL6" s="16"/>
+      <c r="BM6" s="16"/>
+      <c r="BN6" s="16"/>
+      <c r="BO6" s="16"/>
+      <c r="BP6" s="16"/>
+      <c r="BQ6" s="16"/>
+      <c r="BR6" s="16"/>
+      <c r="BS6" s="16"/>
+      <c r="BT6" s="16"/>
+      <c r="BU6" s="16"/>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16">
         <v>393.04199999999997</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16">
         <v>410.44200000000001</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="3"/>
-      <c r="AI7" s="3"/>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
-      <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
-      <c r="AO7" s="3"/>
-      <c r="AP7" s="3"/>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="3"/>
-      <c r="AS7" s="3"/>
-      <c r="AT7" s="3"/>
-      <c r="AU7" s="3"/>
-      <c r="AV7" s="3"/>
-      <c r="AW7" s="3"/>
-      <c r="AX7" s="3"/>
-      <c r="AY7" s="3"/>
-      <c r="AZ7" s="3"/>
-    </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16">
+        <v>359.78800000000001</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16">
+        <v>480.82600000000002</v>
+      </c>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="16"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
+      <c r="AL7" s="16"/>
+      <c r="AM7" s="16"/>
+      <c r="AN7" s="16"/>
+      <c r="AO7" s="16"/>
+      <c r="AP7" s="16"/>
+      <c r="AQ7" s="16"/>
+      <c r="AR7" s="16"/>
+      <c r="AS7" s="16"/>
+      <c r="AT7" s="16"/>
+      <c r="AU7" s="16"/>
+      <c r="AV7" s="16"/>
+      <c r="AW7" s="16"/>
+      <c r="AX7" s="16"/>
+      <c r="AY7" s="16"/>
+      <c r="AZ7" s="16"/>
+      <c r="BA7" s="16"/>
+      <c r="BB7" s="16"/>
+      <c r="BC7" s="16"/>
+      <c r="BD7" s="16"/>
+      <c r="BE7" s="16"/>
+      <c r="BF7" s="16"/>
+      <c r="BG7" s="16"/>
+      <c r="BH7" s="16"/>
+      <c r="BI7" s="16"/>
+      <c r="BJ7" s="16"/>
+      <c r="BK7" s="16"/>
+      <c r="BL7" s="16"/>
+      <c r="BM7" s="16"/>
+      <c r="BN7" s="16"/>
+      <c r="BO7" s="16"/>
+      <c r="BP7" s="16"/>
+      <c r="BQ7" s="16"/>
+      <c r="BR7" s="16"/>
+      <c r="BS7" s="16"/>
+      <c r="BT7" s="16"/>
+      <c r="BU7" s="16"/>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9">
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17">
         <v>1301.0550000000001</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17">
         <v>1289.0940000000001</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="3"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="3"/>
-      <c r="AQ8" s="3"/>
-      <c r="AR8" s="3"/>
-      <c r="AS8" s="3"/>
-      <c r="AT8" s="3"/>
-      <c r="AU8" s="3"/>
-      <c r="AV8" s="3"/>
-      <c r="AW8" s="3"/>
-      <c r="AX8" s="3"/>
-      <c r="AY8" s="3"/>
-      <c r="AZ8" s="3"/>
-    </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J8" s="17"/>
+      <c r="K8" s="17">
+        <v>1089.5989999999999</v>
+      </c>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="17">
+        <v>1195.2850000000001</v>
+      </c>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="16"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16"/>
+      <c r="AO8" s="16"/>
+      <c r="AP8" s="16"/>
+      <c r="AQ8" s="16"/>
+      <c r="AR8" s="16"/>
+      <c r="AS8" s="16"/>
+      <c r="AT8" s="16"/>
+      <c r="AU8" s="16"/>
+      <c r="AV8" s="16"/>
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="16"/>
+      <c r="AY8" s="16"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="16"/>
+      <c r="BB8" s="16"/>
+      <c r="BC8" s="16"/>
+      <c r="BD8" s="16"/>
+      <c r="BE8" s="16"/>
+      <c r="BF8" s="16"/>
+      <c r="BG8" s="16"/>
+      <c r="BH8" s="16"/>
+      <c r="BI8" s="16"/>
+      <c r="BJ8" s="16"/>
+      <c r="BK8" s="16"/>
+      <c r="BL8" s="16"/>
+      <c r="BM8" s="16"/>
+      <c r="BN8" s="16"/>
+      <c r="BO8" s="16"/>
+      <c r="BP8" s="16"/>
+      <c r="BQ8" s="16"/>
+      <c r="BR8" s="16"/>
+      <c r="BS8" s="16"/>
+      <c r="BT8" s="16"/>
+      <c r="BU8" s="16"/>
+    </row>
+    <row r="9" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3">
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16">
         <v>757.25800000000004</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3">
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16">
         <v>762.47</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="3"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
-      <c r="AS9" s="3"/>
-      <c r="AT9" s="3"/>
-      <c r="AU9" s="3"/>
-      <c r="AV9" s="3"/>
-      <c r="AW9" s="3"/>
-      <c r="AX9" s="3"/>
-      <c r="AY9" s="3"/>
-      <c r="AZ9" s="3"/>
-    </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J9" s="16"/>
+      <c r="K9" s="16">
+        <v>767.178</v>
+      </c>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16">
+        <v>739.11300000000006</v>
+      </c>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="16"/>
+      <c r="AM9" s="16"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="16"/>
+      <c r="AP9" s="16"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="16"/>
+      <c r="AS9" s="16"/>
+      <c r="AT9" s="16"/>
+      <c r="AU9" s="16"/>
+      <c r="AV9" s="16"/>
+      <c r="AW9" s="16"/>
+      <c r="AX9" s="16"/>
+      <c r="AY9" s="16"/>
+      <c r="AZ9" s="16"/>
+      <c r="BA9" s="16"/>
+      <c r="BB9" s="16"/>
+      <c r="BC9" s="16"/>
+      <c r="BD9" s="16"/>
+      <c r="BE9" s="16"/>
+      <c r="BF9" s="16"/>
+      <c r="BG9" s="16"/>
+      <c r="BH9" s="16"/>
+      <c r="BI9" s="16"/>
+      <c r="BJ9" s="16"/>
+      <c r="BK9" s="16"/>
+      <c r="BL9" s="16"/>
+      <c r="BM9" s="16"/>
+      <c r="BN9" s="16"/>
+      <c r="BO9" s="16"/>
+      <c r="BP9" s="16"/>
+      <c r="BQ9" s="16"/>
+      <c r="BR9" s="16"/>
+      <c r="BS9" s="16"/>
+      <c r="BT9" s="16"/>
+      <c r="BU9" s="16"/>
+    </row>
+    <row r="10" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="16">
         <f t="shared" ref="C10:H10" si="0">+C8-C9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="16">
         <f t="shared" si="0"/>
         <v>543.79700000000003</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="16">
         <f>+I8-I9</f>
         <v>526.62400000000002</v>
       </c>
-      <c r="J10" s="3">
-        <f t="shared" ref="J10" si="1">+J8-J9</f>
+      <c r="J10" s="16">
+        <f t="shared" ref="J10:O10" si="1">+J8-J9</f>
         <v>0</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="3"/>
-      <c r="AH10" s="3"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="3"/>
-      <c r="AQ10" s="3"/>
-      <c r="AR10" s="3"/>
-      <c r="AS10" s="3"/>
-      <c r="AT10" s="3"/>
-      <c r="AU10" s="3"/>
-      <c r="AV10" s="3"/>
-      <c r="AW10" s="3"/>
-      <c r="AX10" s="3"/>
-      <c r="AY10" s="3"/>
-      <c r="AZ10" s="3"/>
-    </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="K10" s="16">
+        <f t="shared" si="1"/>
+        <v>322.42099999999994</v>
+      </c>
+      <c r="L10" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="16">
+        <f t="shared" si="1"/>
+        <v>456.17200000000003</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="16"/>
+      <c r="AJ10" s="16"/>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="16"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="16"/>
+      <c r="AP10" s="16"/>
+      <c r="AQ10" s="16"/>
+      <c r="AR10" s="16"/>
+      <c r="AS10" s="16"/>
+      <c r="AT10" s="16"/>
+      <c r="AU10" s="16"/>
+      <c r="AV10" s="16"/>
+      <c r="AW10" s="16"/>
+      <c r="AX10" s="16"/>
+      <c r="AY10" s="16"/>
+      <c r="AZ10" s="16"/>
+      <c r="BA10" s="16"/>
+      <c r="BB10" s="16"/>
+      <c r="BC10" s="16"/>
+      <c r="BD10" s="16"/>
+      <c r="BE10" s="16"/>
+      <c r="BF10" s="16"/>
+      <c r="BG10" s="16"/>
+      <c r="BH10" s="16"/>
+      <c r="BI10" s="16"/>
+      <c r="BJ10" s="16"/>
+      <c r="BK10" s="16"/>
+      <c r="BL10" s="16"/>
+      <c r="BM10" s="16"/>
+      <c r="BN10" s="16"/>
+      <c r="BO10" s="16"/>
+      <c r="BP10" s="16"/>
+      <c r="BQ10" s="16"/>
+      <c r="BR10" s="16"/>
+      <c r="BS10" s="16"/>
+      <c r="BT10" s="16"/>
+      <c r="BU10" s="16"/>
+    </row>
+    <row r="11" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16">
         <v>361.99200000000002</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16">
         <v>351.38</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3"/>
-      <c r="AQ11" s="3"/>
-      <c r="AR11" s="3"/>
-      <c r="AS11" s="3"/>
-      <c r="AT11" s="3"/>
-      <c r="AU11" s="3"/>
-      <c r="AV11" s="3"/>
-      <c r="AW11" s="3"/>
-      <c r="AX11" s="3"/>
-      <c r="AY11" s="3"/>
-      <c r="AZ11" s="3"/>
-    </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J11" s="16"/>
+      <c r="K11" s="16">
+        <v>338.786</v>
+      </c>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16">
+        <v>376.49200000000002</v>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="16"/>
+      <c r="AO11" s="16"/>
+      <c r="AP11" s="16"/>
+      <c r="AQ11" s="16"/>
+      <c r="AR11" s="16"/>
+      <c r="AS11" s="16"/>
+      <c r="AT11" s="16"/>
+      <c r="AU11" s="16"/>
+      <c r="AV11" s="16"/>
+      <c r="AW11" s="16"/>
+      <c r="AX11" s="16"/>
+      <c r="AY11" s="16"/>
+      <c r="AZ11" s="16"/>
+      <c r="BA11" s="16"/>
+      <c r="BB11" s="16"/>
+      <c r="BC11" s="16"/>
+      <c r="BD11" s="16"/>
+      <c r="BE11" s="16"/>
+      <c r="BF11" s="16"/>
+      <c r="BG11" s="16"/>
+      <c r="BH11" s="16"/>
+      <c r="BI11" s="16"/>
+      <c r="BJ11" s="16"/>
+      <c r="BK11" s="16"/>
+      <c r="BL11" s="16"/>
+      <c r="BM11" s="16"/>
+      <c r="BN11" s="16"/>
+      <c r="BO11" s="16"/>
+      <c r="BP11" s="16"/>
+      <c r="BQ11" s="16"/>
+      <c r="BR11" s="16"/>
+      <c r="BS11" s="16"/>
+      <c r="BT11" s="16"/>
+      <c r="BU11" s="16"/>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16">
         <v>0</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3">
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16">
         <v>17.561</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3"/>
-      <c r="AR12" s="3"/>
-      <c r="AS12" s="3"/>
-      <c r="AT12" s="3"/>
-      <c r="AU12" s="3"/>
-      <c r="AV12" s="3"/>
-      <c r="AW12" s="3"/>
-      <c r="AX12" s="3"/>
-      <c r="AY12" s="3"/>
-      <c r="AZ12" s="3"/>
-    </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J12" s="16"/>
+      <c r="K12" s="16">
+        <v>17.119</v>
+      </c>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16">
+        <v>0</v>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AP12" s="16"/>
+      <c r="AQ12" s="16"/>
+      <c r="AR12" s="16"/>
+      <c r="AS12" s="16"/>
+      <c r="AT12" s="16"/>
+      <c r="AU12" s="16"/>
+      <c r="AV12" s="16"/>
+      <c r="AW12" s="16"/>
+      <c r="AX12" s="16"/>
+      <c r="AY12" s="16"/>
+      <c r="AZ12" s="16"/>
+      <c r="BA12" s="16"/>
+      <c r="BB12" s="16"/>
+      <c r="BC12" s="16"/>
+      <c r="BD12" s="16"/>
+      <c r="BE12" s="16"/>
+      <c r="BF12" s="16"/>
+      <c r="BG12" s="16"/>
+      <c r="BH12" s="16"/>
+      <c r="BI12" s="16"/>
+      <c r="BJ12" s="16"/>
+      <c r="BK12" s="16"/>
+      <c r="BL12" s="16"/>
+      <c r="BM12" s="16"/>
+      <c r="BN12" s="16"/>
+      <c r="BO12" s="16"/>
+      <c r="BP12" s="16"/>
+      <c r="BQ12" s="16"/>
+      <c r="BR12" s="16"/>
+      <c r="BS12" s="16"/>
+      <c r="BT12" s="16"/>
+      <c r="BU12" s="16"/>
+    </row>
+    <row r="13" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16">
         <v>56.444000000000003</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3">
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16">
         <v>51.594000000000001</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3"/>
-      <c r="AS13" s="3"/>
-      <c r="AT13" s="3"/>
-      <c r="AU13" s="3"/>
-      <c r="AV13" s="3"/>
-      <c r="AW13" s="3"/>
-      <c r="AX13" s="3"/>
-      <c r="AY13" s="3"/>
-      <c r="AZ13" s="3"/>
-    </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J13" s="16"/>
+      <c r="K13" s="16">
+        <v>51.697000000000003</v>
+      </c>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16">
+        <v>51.454000000000001</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
+      <c r="AM13" s="16"/>
+      <c r="AN13" s="16"/>
+      <c r="AO13" s="16"/>
+      <c r="AP13" s="16"/>
+      <c r="AQ13" s="16"/>
+      <c r="AR13" s="16"/>
+      <c r="AS13" s="16"/>
+      <c r="AT13" s="16"/>
+      <c r="AU13" s="16"/>
+      <c r="AV13" s="16"/>
+      <c r="AW13" s="16"/>
+      <c r="AX13" s="16"/>
+      <c r="AY13" s="16"/>
+      <c r="AZ13" s="16"/>
+      <c r="BA13" s="16"/>
+      <c r="BB13" s="16"/>
+      <c r="BC13" s="16"/>
+      <c r="BD13" s="16"/>
+      <c r="BE13" s="16"/>
+      <c r="BF13" s="16"/>
+      <c r="BG13" s="16"/>
+      <c r="BH13" s="16"/>
+      <c r="BI13" s="16"/>
+      <c r="BJ13" s="16"/>
+      <c r="BK13" s="16"/>
+      <c r="BL13" s="16"/>
+      <c r="BM13" s="16"/>
+      <c r="BN13" s="16"/>
+      <c r="BO13" s="16"/>
+      <c r="BP13" s="16"/>
+      <c r="BQ13" s="16"/>
+      <c r="BR13" s="16"/>
+      <c r="BS13" s="16"/>
+      <c r="BT13" s="16"/>
+      <c r="BU13" s="16"/>
+    </row>
+    <row r="14" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="16">
         <f t="shared" ref="C14:H14" si="2">+C10-SUM(C11:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="16">
         <f t="shared" si="2"/>
         <v>125.36099999999999</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="16">
         <f>+I10-SUM(I11:I13)</f>
         <v>106.08900000000006</v>
       </c>
-      <c r="J14" s="3">
-        <f t="shared" ref="J14" si="3">+J10-SUM(J11:J13)</f>
+      <c r="J14" s="16">
+        <f t="shared" ref="J14:O14" si="3">+J10-SUM(J11:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="3"/>
-      <c r="AQ14" s="3"/>
-      <c r="AR14" s="3"/>
-      <c r="AS14" s="3"/>
-      <c r="AT14" s="3"/>
-      <c r="AU14" s="3"/>
-      <c r="AV14" s="3"/>
-      <c r="AW14" s="3"/>
-      <c r="AX14" s="3"/>
-      <c r="AY14" s="3"/>
-      <c r="AZ14" s="3"/>
-    </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="K14" s="16">
+        <f t="shared" si="3"/>
+        <v>-85.18100000000004</v>
+      </c>
+      <c r="L14" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="16">
+        <f t="shared" si="3"/>
+        <v>28.225999999999999</v>
+      </c>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="16"/>
+      <c r="AI14" s="16"/>
+      <c r="AJ14" s="16"/>
+      <c r="AK14" s="16"/>
+      <c r="AL14" s="16"/>
+      <c r="AM14" s="16"/>
+      <c r="AN14" s="16"/>
+      <c r="AO14" s="16"/>
+      <c r="AP14" s="16"/>
+      <c r="AQ14" s="16"/>
+      <c r="AR14" s="16"/>
+      <c r="AS14" s="16"/>
+      <c r="AT14" s="16"/>
+      <c r="AU14" s="16"/>
+      <c r="AV14" s="16"/>
+      <c r="AW14" s="16"/>
+      <c r="AX14" s="16"/>
+      <c r="AY14" s="16"/>
+      <c r="AZ14" s="16"/>
+      <c r="BA14" s="16"/>
+      <c r="BB14" s="16"/>
+      <c r="BC14" s="16"/>
+      <c r="BD14" s="16"/>
+      <c r="BE14" s="16"/>
+      <c r="BF14" s="16"/>
+      <c r="BG14" s="16"/>
+      <c r="BH14" s="16"/>
+      <c r="BI14" s="16"/>
+      <c r="BJ14" s="16"/>
+      <c r="BK14" s="16"/>
+      <c r="BL14" s="16"/>
+      <c r="BM14" s="16"/>
+      <c r="BN14" s="16"/>
+      <c r="BO14" s="16"/>
+      <c r="BP14" s="16"/>
+      <c r="BQ14" s="16"/>
+      <c r="BR14" s="16"/>
+      <c r="BS14" s="16"/>
+      <c r="BT14" s="16"/>
+      <c r="BU14" s="16"/>
+    </row>
+    <row r="15" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3">
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16">
         <v>2.871</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16">
         <v>1.246</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="3"/>
-      <c r="AH15" s="3"/>
-      <c r="AI15" s="3"/>
-      <c r="AJ15" s="3"/>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="3"/>
-      <c r="AM15" s="3"/>
-      <c r="AN15" s="3"/>
-      <c r="AO15" s="3"/>
-      <c r="AP15" s="3"/>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3"/>
-      <c r="AS15" s="3"/>
-      <c r="AT15" s="3"/>
-      <c r="AU15" s="3"/>
-      <c r="AV15" s="3"/>
-      <c r="AW15" s="3"/>
-      <c r="AX15" s="3"/>
-      <c r="AY15" s="3"/>
-      <c r="AZ15" s="3"/>
-    </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="J15" s="16"/>
+      <c r="K15" s="16">
+        <v>0.219</v>
+      </c>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16">
+        <v>-7.8529999999999998</v>
+      </c>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="16"/>
+      <c r="AI15" s="16"/>
+      <c r="AJ15" s="16"/>
+      <c r="AK15" s="16"/>
+      <c r="AL15" s="16"/>
+      <c r="AM15" s="16"/>
+      <c r="AN15" s="16"/>
+      <c r="AO15" s="16"/>
+      <c r="AP15" s="16"/>
+      <c r="AQ15" s="16"/>
+      <c r="AR15" s="16"/>
+      <c r="AS15" s="16"/>
+      <c r="AT15" s="16"/>
+      <c r="AU15" s="16"/>
+      <c r="AV15" s="16"/>
+      <c r="AW15" s="16"/>
+      <c r="AX15" s="16"/>
+      <c r="AY15" s="16"/>
+      <c r="AZ15" s="16"/>
+      <c r="BA15" s="16"/>
+      <c r="BB15" s="16"/>
+      <c r="BC15" s="16"/>
+      <c r="BD15" s="16"/>
+      <c r="BE15" s="16"/>
+      <c r="BF15" s="16"/>
+      <c r="BG15" s="16"/>
+      <c r="BH15" s="16"/>
+      <c r="BI15" s="16"/>
+      <c r="BJ15" s="16"/>
+      <c r="BK15" s="16"/>
+      <c r="BL15" s="16"/>
+      <c r="BM15" s="16"/>
+      <c r="BN15" s="16"/>
+      <c r="BO15" s="16"/>
+      <c r="BP15" s="16"/>
+      <c r="BQ15" s="16"/>
+      <c r="BR15" s="16"/>
+      <c r="BS15" s="16"/>
+      <c r="BT15" s="16"/>
+      <c r="BU15" s="16"/>
+    </row>
+    <row r="16" spans="1:73" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3">
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16">
         <v>3.984</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3">
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16">
         <v>0.89500000000000002</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3"/>
-      <c r="AG16" s="3"/>
-      <c r="AH16" s="3"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3"/>
-      <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="3"/>
-      <c r="AS16" s="3"/>
-      <c r="AT16" s="3"/>
-      <c r="AU16" s="3"/>
-      <c r="AV16" s="3"/>
-      <c r="AW16" s="3"/>
-      <c r="AX16" s="3"/>
-      <c r="AY16" s="3"/>
-      <c r="AZ16" s="3"/>
-    </row>
-    <row r="17" spans="2:52" x14ac:dyDescent="0.2">
+      <c r="J16" s="16"/>
+      <c r="K16" s="16">
+        <v>-0.16800000000000001</v>
+      </c>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16">
+        <v>7.22</v>
+      </c>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="16"/>
+      <c r="AI16" s="16"/>
+      <c r="AJ16" s="16"/>
+      <c r="AK16" s="16"/>
+      <c r="AL16" s="16"/>
+      <c r="AM16" s="16"/>
+      <c r="AN16" s="16"/>
+      <c r="AO16" s="16"/>
+      <c r="AP16" s="16"/>
+      <c r="AQ16" s="16"/>
+      <c r="AR16" s="16"/>
+      <c r="AS16" s="16"/>
+      <c r="AT16" s="16"/>
+      <c r="AU16" s="16"/>
+      <c r="AV16" s="16"/>
+      <c r="AW16" s="16"/>
+      <c r="AX16" s="16"/>
+      <c r="AY16" s="16"/>
+      <c r="AZ16" s="16"/>
+      <c r="BA16" s="16"/>
+      <c r="BB16" s="16"/>
+      <c r="BC16" s="16"/>
+      <c r="BD16" s="16"/>
+      <c r="BE16" s="16"/>
+      <c r="BF16" s="16"/>
+      <c r="BG16" s="16"/>
+      <c r="BH16" s="16"/>
+      <c r="BI16" s="16"/>
+      <c r="BJ16" s="16"/>
+      <c r="BK16" s="16"/>
+      <c r="BL16" s="16"/>
+      <c r="BM16" s="16"/>
+      <c r="BN16" s="16"/>
+      <c r="BO16" s="16"/>
+      <c r="BP16" s="16"/>
+      <c r="BQ16" s="16"/>
+      <c r="BR16" s="16"/>
+      <c r="BS16" s="16"/>
+      <c r="BT16" s="16"/>
+      <c r="BU16" s="16"/>
+    </row>
+    <row r="17" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="16">
         <f t="shared" ref="C17:H17" si="4">+C14+C15+C16</f>
         <v>0</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="16">
         <f t="shared" si="4"/>
         <v>132.21600000000001</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="16">
         <f>+I14+I15+I16</f>
         <v>108.23000000000005</v>
       </c>
-      <c r="J17" s="3">
-        <f t="shared" ref="J17" si="5">+J14+J15+J16</f>
+      <c r="J17" s="16">
+        <f t="shared" ref="J17:O17" si="5">+J14+J15+J16</f>
         <v>0</v>
       </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="3"/>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
-      <c r="AJ17" s="3"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="3"/>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3"/>
-      <c r="AS17" s="3"/>
-      <c r="AT17" s="3"/>
-      <c r="AU17" s="3"/>
-      <c r="AV17" s="3"/>
-      <c r="AW17" s="3"/>
-      <c r="AX17" s="3"/>
-      <c r="AY17" s="3"/>
-      <c r="AZ17" s="3"/>
-    </row>
-    <row r="18" spans="2:52" x14ac:dyDescent="0.2">
+      <c r="K17" s="16">
+        <f t="shared" si="5"/>
+        <v>-85.130000000000052</v>
+      </c>
+      <c r="L17" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="16">
+        <f t="shared" si="5"/>
+        <v>27.592999999999996</v>
+      </c>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="16"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="16"/>
+      <c r="AP17" s="16"/>
+      <c r="AQ17" s="16"/>
+      <c r="AR17" s="16"/>
+      <c r="AS17" s="16"/>
+      <c r="AT17" s="16"/>
+      <c r="AU17" s="16"/>
+      <c r="AV17" s="16"/>
+      <c r="AW17" s="16"/>
+      <c r="AX17" s="16"/>
+      <c r="AY17" s="16"/>
+      <c r="AZ17" s="16"/>
+      <c r="BA17" s="16"/>
+      <c r="BB17" s="16"/>
+      <c r="BC17" s="16"/>
+      <c r="BD17" s="16"/>
+      <c r="BE17" s="16"/>
+      <c r="BF17" s="16"/>
+      <c r="BG17" s="16"/>
+      <c r="BH17" s="16"/>
+      <c r="BI17" s="16"/>
+      <c r="BJ17" s="16"/>
+      <c r="BK17" s="16"/>
+      <c r="BL17" s="16"/>
+      <c r="BM17" s="16"/>
+      <c r="BN17" s="16"/>
+      <c r="BO17" s="16"/>
+      <c r="BP17" s="16"/>
+      <c r="BQ17" s="16"/>
+      <c r="BR17" s="16"/>
+      <c r="BS17" s="16"/>
+      <c r="BT17" s="16"/>
+      <c r="BU17" s="16"/>
+    </row>
+    <row r="18" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3">
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16">
         <v>35.515999999999998</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3">
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16">
         <v>28.210999999999999</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="3"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
-      <c r="AJ18" s="3"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="3"/>
-      <c r="AM18" s="3"/>
-      <c r="AN18" s="3"/>
-      <c r="AO18" s="3"/>
-      <c r="AP18" s="3"/>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
-      <c r="AS18" s="3"/>
-      <c r="AT18" s="3"/>
-      <c r="AU18" s="3"/>
-      <c r="AV18" s="3"/>
-      <c r="AW18" s="3"/>
-      <c r="AX18" s="3"/>
-      <c r="AY18" s="3"/>
-      <c r="AZ18" s="3"/>
-    </row>
-    <row r="19" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
+      <c r="J18" s="16"/>
+      <c r="K18" s="16">
+        <v>-19.712</v>
+      </c>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16">
+        <v>4.6580000000000004</v>
+      </c>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="16"/>
+      <c r="AB18" s="16"/>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="16"/>
+      <c r="AI18" s="16"/>
+      <c r="AJ18" s="16"/>
+      <c r="AK18" s="16"/>
+      <c r="AL18" s="16"/>
+      <c r="AM18" s="16"/>
+      <c r="AN18" s="16"/>
+      <c r="AO18" s="16"/>
+      <c r="AP18" s="16"/>
+      <c r="AQ18" s="16"/>
+      <c r="AR18" s="16"/>
+      <c r="AS18" s="16"/>
+      <c r="AT18" s="16"/>
+      <c r="AU18" s="16"/>
+      <c r="AV18" s="16"/>
+      <c r="AW18" s="16"/>
+      <c r="AX18" s="16"/>
+      <c r="AY18" s="16"/>
+      <c r="AZ18" s="16"/>
+      <c r="BA18" s="16"/>
+      <c r="BB18" s="16"/>
+      <c r="BC18" s="16"/>
+      <c r="BD18" s="16"/>
+      <c r="BE18" s="16"/>
+      <c r="BF18" s="16"/>
+      <c r="BG18" s="16"/>
+      <c r="BH18" s="16"/>
+      <c r="BI18" s="16"/>
+      <c r="BJ18" s="16"/>
+      <c r="BK18" s="16"/>
+      <c r="BL18" s="16"/>
+      <c r="BM18" s="16"/>
+      <c r="BN18" s="16"/>
+      <c r="BO18" s="16"/>
+      <c r="BP18" s="16"/>
+      <c r="BQ18" s="16"/>
+      <c r="BR18" s="16"/>
+      <c r="BS18" s="16"/>
+      <c r="BT18" s="16"/>
+      <c r="BU18" s="16"/>
+    </row>
+    <row r="19" spans="2:73" x14ac:dyDescent="0.2">
+      <c r="B19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="16">
         <f t="shared" ref="C19:H19" si="6">+C17-C18</f>
         <v>0</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="16">
         <f t="shared" si="6"/>
         <v>96.700000000000017</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="16">
         <f>+I17-I18</f>
         <v>80.019000000000048</v>
       </c>
-      <c r="J19" s="3">
-        <f t="shared" ref="J19" si="7">+J17-J18</f>
+      <c r="J19" s="16">
+        <f t="shared" ref="J19:O19" si="7">+J17-J18</f>
         <v>0</v>
       </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3"/>
-      <c r="AS19" s="3"/>
-      <c r="AT19" s="3"/>
-      <c r="AU19" s="3"/>
-      <c r="AV19" s="3"/>
-      <c r="AW19" s="3"/>
-      <c r="AX19" s="3"/>
-      <c r="AY19" s="3"/>
-      <c r="AZ19" s="3"/>
-    </row>
-    <row r="20" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="3"/>
-      <c r="AF20" s="3"/>
-      <c r="AG20" s="3"/>
-      <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
-      <c r="AJ20" s="3"/>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3"/>
-      <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
-      <c r="AO20" s="3"/>
-      <c r="AP20" s="3"/>
-      <c r="AQ20" s="3"/>
-      <c r="AR20" s="3"/>
-      <c r="AS20" s="3"/>
-      <c r="AT20" s="3"/>
-      <c r="AU20" s="3"/>
-      <c r="AV20" s="3"/>
-      <c r="AW20" s="3"/>
-      <c r="AX20" s="3"/>
-      <c r="AY20" s="3"/>
-      <c r="AZ20" s="3"/>
-    </row>
-    <row r="21" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="10" t="e">
-        <f t="shared" ref="C21:H21" si="8">+C19/C22</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D21" s="10" t="e">
+      <c r="K19" s="16">
+        <f t="shared" si="7"/>
+        <v>-65.418000000000049</v>
+      </c>
+      <c r="L19" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="16">
+        <f t="shared" si="7"/>
+        <v>22.934999999999995</v>
+      </c>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
+      <c r="AI19" s="16"/>
+      <c r="AJ19" s="16"/>
+      <c r="AK19" s="16"/>
+      <c r="AL19" s="16"/>
+      <c r="AM19" s="16"/>
+      <c r="AN19" s="16"/>
+      <c r="AO19" s="16"/>
+      <c r="AP19" s="16"/>
+      <c r="AQ19" s="16"/>
+      <c r="AR19" s="16"/>
+      <c r="AS19" s="16"/>
+      <c r="AT19" s="16"/>
+      <c r="AU19" s="16"/>
+      <c r="AV19" s="16"/>
+      <c r="AW19" s="16"/>
+      <c r="AX19" s="16"/>
+      <c r="AY19" s="16"/>
+      <c r="AZ19" s="16"/>
+      <c r="BA19" s="16"/>
+      <c r="BB19" s="16"/>
+      <c r="BC19" s="16"/>
+      <c r="BD19" s="16"/>
+      <c r="BE19" s="16"/>
+      <c r="BF19" s="16"/>
+      <c r="BG19" s="16"/>
+      <c r="BH19" s="16"/>
+      <c r="BI19" s="16"/>
+      <c r="BJ19" s="16"/>
+      <c r="BK19" s="16"/>
+      <c r="BL19" s="16"/>
+      <c r="BM19" s="16"/>
+      <c r="BN19" s="16"/>
+      <c r="BO19" s="16"/>
+      <c r="BP19" s="16"/>
+      <c r="BQ19" s="16"/>
+      <c r="BR19" s="16"/>
+      <c r="BS19" s="16"/>
+      <c r="BT19" s="16"/>
+      <c r="BU19" s="16"/>
+    </row>
+    <row r="20" spans="2:73" x14ac:dyDescent="0.2">
+      <c r="B20" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16">
+        <v>0</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16">
+        <v>-0.51900000000000002</v>
+      </c>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16">
+        <v>-0.55800000000000005</v>
+      </c>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
+      <c r="AK20" s="16"/>
+      <c r="AL20" s="16"/>
+      <c r="AM20" s="16"/>
+      <c r="AN20" s="16"/>
+      <c r="AO20" s="16"/>
+      <c r="AP20" s="16"/>
+      <c r="AQ20" s="16"/>
+      <c r="AR20" s="16"/>
+      <c r="AS20" s="16"/>
+      <c r="AT20" s="16"/>
+      <c r="AU20" s="16"/>
+      <c r="AV20" s="16"/>
+      <c r="AW20" s="16"/>
+      <c r="AX20" s="16"/>
+      <c r="AY20" s="16"/>
+      <c r="AZ20" s="16"/>
+      <c r="BA20" s="16"/>
+      <c r="BB20" s="16"/>
+      <c r="BC20" s="16"/>
+      <c r="BD20" s="16"/>
+      <c r="BE20" s="16"/>
+      <c r="BF20" s="16"/>
+      <c r="BG20" s="16"/>
+      <c r="BH20" s="16"/>
+      <c r="BI20" s="16"/>
+      <c r="BJ20" s="16"/>
+      <c r="BK20" s="16"/>
+      <c r="BL20" s="16"/>
+      <c r="BM20" s="16"/>
+      <c r="BN20" s="16"/>
+      <c r="BO20" s="16"/>
+      <c r="BP20" s="16"/>
+      <c r="BQ20" s="16"/>
+      <c r="BR20" s="16"/>
+      <c r="BS20" s="16"/>
+      <c r="BT20" s="16"/>
+      <c r="BU20" s="16"/>
+    </row>
+    <row r="21" spans="2:73" x14ac:dyDescent="0.2">
+      <c r="B21" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="16">
+        <f t="shared" ref="C21:D21" si="8">+C19-C20</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="16">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="10">
-        <f t="shared" si="8"/>
-        <v>0.4950266966310542</v>
-      </c>
-      <c r="F21" s="10" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="10" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="10" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I21" s="10">
-        <f>+I19/I22</f>
-        <v>0.4176291602949852</v>
-      </c>
-      <c r="J21" s="10" t="e">
-        <f t="shared" ref="J21" si="9">+J19/J22</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="3"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="3"/>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="3"/>
-      <c r="AS21" s="3"/>
-      <c r="AT21" s="3"/>
-      <c r="AU21" s="3"/>
-      <c r="AV21" s="3"/>
-      <c r="AW21" s="3"/>
-      <c r="AX21" s="3"/>
-      <c r="AY21" s="3"/>
-      <c r="AZ21" s="3"/>
-    </row>
-    <row r="22" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" s="16">
+        <f>+E19-E20</f>
+        <v>96.700000000000017</v>
+      </c>
+      <c r="F21" s="16">
+        <f t="shared" ref="F21:R21" si="9">+F19-F20</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="9"/>
+        <v>80.019000000000048</v>
+      </c>
+      <c r="J21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="16">
+        <f t="shared" si="9"/>
+        <v>-64.899000000000044</v>
+      </c>
+      <c r="L21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="16">
+        <f t="shared" si="9"/>
+        <v>23.492999999999995</v>
+      </c>
+      <c r="P21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="16"/>
+      <c r="AI21" s="16"/>
+      <c r="AJ21" s="16"/>
+      <c r="AK21" s="16"/>
+      <c r="AL21" s="16"/>
+      <c r="AM21" s="16"/>
+      <c r="AN21" s="16"/>
+      <c r="AO21" s="16"/>
+      <c r="AP21" s="16"/>
+      <c r="AQ21" s="16"/>
+      <c r="AR21" s="16"/>
+      <c r="AS21" s="16"/>
+      <c r="AT21" s="16"/>
+      <c r="AU21" s="16"/>
+      <c r="AV21" s="16"/>
+      <c r="AW21" s="16"/>
+      <c r="AX21" s="16"/>
+      <c r="AY21" s="16"/>
+      <c r="AZ21" s="16"/>
+      <c r="BA21" s="16"/>
+      <c r="BB21" s="16"/>
+      <c r="BC21" s="16"/>
+      <c r="BD21" s="16"/>
+      <c r="BE21" s="16"/>
+      <c r="BF21" s="16"/>
+      <c r="BG21" s="16"/>
+      <c r="BH21" s="16"/>
+      <c r="BI21" s="16"/>
+      <c r="BJ21" s="16"/>
+      <c r="BK21" s="16"/>
+      <c r="BL21" s="16"/>
+      <c r="BM21" s="16"/>
+      <c r="BN21" s="16"/>
+      <c r="BO21" s="16"/>
+      <c r="BP21" s="16"/>
+      <c r="BQ21" s="16"/>
+      <c r="BR21" s="16"/>
+      <c r="BS21" s="16"/>
+      <c r="BT21" s="16"/>
+      <c r="BU21" s="16"/>
+    </row>
+    <row r="22" spans="2:73" x14ac:dyDescent="0.2">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="3">
-        <v>195.34299999999999</v>
-      </c>
+      <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3">
-        <v>191.60300000000001</v>
-      </c>
+      <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -1939,20 +2476,62 @@
       <c r="AY22" s="3"/>
       <c r="AZ22" s="3"/>
     </row>
-    <row r="23" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
+    <row r="23" spans="2:73" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="10" t="e">
+        <f t="shared" ref="C23:H23" si="10">+C21/C24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D23" s="18" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E23" s="18">
+        <f t="shared" si="10"/>
+        <v>0.4950266966310542</v>
+      </c>
+      <c r="F23" s="18" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="18" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H23" s="18" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I23" s="18">
+        <f>+I21/I24</f>
+        <v>0.4176291602949852</v>
+      </c>
+      <c r="J23" s="18" t="e">
+        <f t="shared" ref="J23" si="11">+J21/J24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K23" s="18">
+        <f t="shared" ref="K23" si="12">+K21/K24</f>
+        <v>-0.36145766034709403</v>
+      </c>
+      <c r="L23" s="18" t="e">
+        <f t="shared" ref="L23" si="13">+L21/L24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M23" s="18" t="e">
+        <f t="shared" ref="M23" si="14">+M21/M24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N23" s="18" t="e">
+        <f t="shared" ref="N23" si="15">+N21/N24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O23" s="18">
+        <f t="shared" ref="O23" si="16">+O21/O24</f>
+        <v>0.13997676289212616</v>
+      </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -1991,35 +2570,31 @@
       <c r="AY23" s="3"/>
       <c r="AZ23" s="3"/>
     </row>
-    <row r="24" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="E24" s="3">
+        <v>195.34299999999999</v>
+      </c>
       <c r="F24" s="3"/>
-      <c r="G24" s="11" t="e">
-        <f t="shared" ref="G24:H24" si="10">+G3/C3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H24" s="11" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I24" s="11">
-        <f>+I3/E3-1</f>
-        <v>-1.0842368640533784E-2</v>
-      </c>
-      <c r="J24" s="11" t="e">
-        <f>+J3/F3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3">
+        <v>191.60300000000001</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3">
+        <v>179.548</v>
+      </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="O24" s="3">
+        <v>167.83500000000001</v>
+      </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -2058,30 +2633,15 @@
       <c r="AY24" s="3"/>
       <c r="AZ24" s="3"/>
     </row>
-    <row r="25" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
+    <row r="25" spans="2:73" x14ac:dyDescent="0.2">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="11" t="e">
-        <f t="shared" ref="G25:H25" si="11">+G4/C4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H25" s="11" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I25" s="11">
-        <f>+I4/E4-1</f>
-        <v>-6.9548615846174444E-3</v>
-      </c>
-      <c r="J25" s="11" t="e">
-        <f>+J4/F4-1</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -2125,38 +2685,62 @@
       <c r="AY25" s="3"/>
       <c r="AZ25" s="3"/>
     </row>
-    <row r="26" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="11" t="e">
-        <f t="shared" ref="G26:H28" si="12">+G6/C6-1</f>
+        <f t="shared" ref="G26:H26" si="17">+G3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H26" s="11" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="11">
-        <f>+I6/E6-1</f>
-        <v>-2.9699852340507982E-2</v>
+        <f>+I3/E3-1</f>
+        <v>-1.0842368640533784E-2</v>
       </c>
       <c r="J26" s="11" t="e">
-        <f>+J6/F6-1</f>
+        <f>+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
+      <c r="K26" s="11" t="e">
+        <f t="shared" ref="K26:R26" si="18">+K3/G3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L26" s="11" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M26" s="11">
+        <f t="shared" si="18"/>
+        <v>-1</v>
+      </c>
+      <c r="N26" s="11" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="11">
+        <f t="shared" si="18"/>
+        <v>-5.1020408163264808E-3</v>
+      </c>
+      <c r="P26" s="11" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q26" s="11" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R26" s="11" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -2192,38 +2776,62 @@
       <c r="AY26" s="3"/>
       <c r="AZ26" s="3"/>
     </row>
-    <row r="27" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="11" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G27:H27" si="19">+G4/C4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H27" s="11" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" ref="I27:J28" si="13">+I7/E7-1</f>
-        <v>4.4270078006930724E-2</v>
+        <f>+I4/E4-1</f>
+        <v>-6.9548615846174444E-3</v>
       </c>
       <c r="J27" s="11" t="e">
-        <f t="shared" si="13"/>
+        <f>+J4/F4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
+      <c r="K27" s="11" t="e">
+        <f t="shared" ref="K27:R27" si="20">+K4/G4-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L27" s="11" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M27" s="11">
+        <f t="shared" si="20"/>
+        <v>-1</v>
+      </c>
+      <c r="N27" s="11" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="11">
+        <f t="shared" si="20"/>
+        <v>-1.6592920353982743E-3</v>
+      </c>
+      <c r="P27" s="11" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q27" s="11" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R27" s="11" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -2259,38 +2867,62 @@
       <c r="AY27" s="3"/>
       <c r="AZ27" s="3"/>
     </row>
-    <row r="28" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="11" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G28:H30" si="21">+G6/C6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="11" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="13"/>
-        <v>-9.1933085073268028E-3</v>
+        <f>+I6/E6-1</f>
+        <v>-2.9699852340507982E-2</v>
       </c>
       <c r="J28" s="11" t="e">
-        <f t="shared" si="13"/>
+        <f>+J6/F6-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
+      <c r="K28" s="11" t="e">
+        <f t="shared" ref="K28:R30" si="22">+K6/G6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L28" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M28" s="11">
+        <f t="shared" si="22"/>
+        <v>-1</v>
+      </c>
+      <c r="N28" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="11">
+        <f t="shared" si="22"/>
+        <v>-2.2178665878809345E-2</v>
+      </c>
+      <c r="P28" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q28" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R28" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -2326,50 +2958,62 @@
       <c r="AY28" s="3"/>
       <c r="AZ28" s="3"/>
     </row>
-    <row r="29" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="11" t="e">
-        <f t="shared" ref="C29:H29" si="14">+C10/C8</f>
+        <v>39</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="11" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="D29" s="11" t="e">
-        <f t="shared" si="14"/>
+      <c r="H29" s="11" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E29" s="11">
-        <f t="shared" si="14"/>
-        <v>0.41796618897740678</v>
-      </c>
-      <c r="F29" s="11" t="e">
-        <f t="shared" si="14"/>
+      <c r="I29" s="11">
+        <f t="shared" ref="I29:J30" si="23">+I7/E7-1</f>
+        <v>4.4270078006930724E-2</v>
+      </c>
+      <c r="J29" s="11" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G29" s="11" t="e">
-        <f t="shared" si="14"/>
+      <c r="K29" s="11" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="11" t="e">
-        <f t="shared" si="14"/>
+      <c r="L29" s="11" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I29" s="11">
-        <f>+I10/I8</f>
-        <v>0.40852257476956683</v>
-      </c>
-      <c r="J29" s="11" t="e">
-        <f>+J10/J8</f>
+      <c r="M29" s="11">
+        <f t="shared" si="22"/>
+        <v>-1</v>
+      </c>
+      <c r="N29" s="11" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
+      <c r="O29" s="11">
+        <f t="shared" si="22"/>
+        <v>0.33641477759124827</v>
+      </c>
+      <c r="P29" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q29" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R29" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -2405,50 +3049,62 @@
       <c r="AY29" s="3"/>
       <c r="AZ29" s="3"/>
     </row>
-    <row r="30" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="11" t="e">
-        <f t="shared" ref="C30:H30" si="15">+C14/C8</f>
+    <row r="30" spans="2:73" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="15" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="D30" s="11" t="e">
-        <f t="shared" si="15"/>
+      <c r="H30" s="15" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E30" s="11">
-        <f t="shared" si="15"/>
-        <v>9.6353344016970835E-2</v>
-      </c>
-      <c r="F30" s="11" t="e">
-        <f t="shared" si="15"/>
+      <c r="I30" s="15">
+        <f t="shared" si="23"/>
+        <v>-9.1933085073268028E-3</v>
+      </c>
+      <c r="J30" s="15" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G30" s="11" t="e">
-        <f t="shared" si="15"/>
+      <c r="K30" s="15" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="11" t="e">
-        <f t="shared" si="15"/>
+      <c r="L30" s="15" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I30" s="11">
-        <f>+I14/I8</f>
-        <v>8.2297334406955622E-2</v>
-      </c>
-      <c r="J30" s="11" t="e">
-        <f>+J14/J8</f>
+      <c r="M30" s="15">
+        <f t="shared" si="22"/>
+        <v>-1</v>
+      </c>
+      <c r="N30" s="15" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
+      <c r="O30" s="15">
+        <f t="shared" si="22"/>
+        <v>9.6995316625657857E-2</v>
+      </c>
+      <c r="P30" s="15" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q30" s="15" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R30" s="15" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -2484,50 +3140,74 @@
       <c r="AY30" s="3"/>
       <c r="AZ30" s="3"/>
     </row>
-    <row r="31" spans="2:52" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:73" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C31" s="11" t="e">
-        <f t="shared" ref="C31:H31" si="16">+C18/C17</f>
+        <f t="shared" ref="C31:H31" si="24">+C10/C8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="11">
-        <f t="shared" si="16"/>
-        <v>0.26862104435166695</v>
+        <f t="shared" si="24"/>
+        <v>0.41796618897740678</v>
       </c>
       <c r="F31" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="11" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="11">
-        <f>+I18/I17</f>
-        <v>0.26065785826480631</v>
+        <f>+I10/I8</f>
+        <v>0.40852257476956683</v>
       </c>
       <c r="J31" s="11" t="e">
-        <f>+J18/J17</f>
+        <f>+J10/J8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
+      <c r="K31" s="11">
+        <f t="shared" ref="K31:R31" si="25">+K10/K8</f>
+        <v>0.29590794411522031</v>
+      </c>
+      <c r="L31" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O31" s="11">
+        <f t="shared" si="25"/>
+        <v>0.38164287178371686</v>
+      </c>
+      <c r="P31" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q31" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R31" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
@@ -2563,23 +3243,74 @@
       <c r="AY31" s="3"/>
       <c r="AZ31" s="3"/>
     </row>
-    <row r="32" spans="2:52" x14ac:dyDescent="0.2">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
+    <row r="32" spans="2:73" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="11" t="e">
+        <f t="shared" ref="C32:H32" si="26">+C14/C8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D32" s="11" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" s="11">
+        <f t="shared" si="26"/>
+        <v>9.6353344016970835E-2</v>
+      </c>
+      <c r="F32" s="11" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="11" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H32" s="11" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I32" s="11">
+        <f>+I14/I8</f>
+        <v>8.2297334406955622E-2</v>
+      </c>
+      <c r="J32" s="11" t="e">
+        <f>+J14/J8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K32" s="11">
+        <f t="shared" ref="K32:R32" si="27">+K14/K8</f>
+        <v>-7.8176466755200805E-2</v>
+      </c>
+      <c r="L32" s="11" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M32" s="11" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" s="11" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O32" s="11">
+        <f t="shared" si="27"/>
+        <v>2.3614451783465867E-2</v>
+      </c>
+      <c r="P32" s="11" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q32" s="11" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" s="11" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
@@ -2615,23 +3346,74 @@
       <c r="AY32" s="3"/>
       <c r="AZ32" s="3"/>
     </row>
-    <row r="33" spans="3:52" x14ac:dyDescent="0.2">
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
+    <row r="33" spans="2:52" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="11" t="e">
+        <f t="shared" ref="C33:H33" si="28">+C18/C17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D33" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E33" s="11">
+        <f t="shared" si="28"/>
+        <v>0.26862104435166695</v>
+      </c>
+      <c r="F33" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G33" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H33" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I33" s="11">
+        <f>+I18/I17</f>
+        <v>0.26065785826480631</v>
+      </c>
+      <c r="J33" s="11" t="e">
+        <f>+J18/J17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K33" s="11">
+        <f t="shared" ref="K33:R33" si="29">+K18/K17</f>
+        <v>0.23155174439093137</v>
+      </c>
+      <c r="L33" s="11" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M33" s="11" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" s="11" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O33" s="11">
+        <f t="shared" si="29"/>
+        <v>0.1688109303084116</v>
+      </c>
+      <c r="P33" s="11" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q33" s="11" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" s="11" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -2667,7 +3449,7 @@
       <c r="AY33" s="3"/>
       <c r="AZ33" s="3"/>
     </row>
-    <row r="34" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -2719,7 +3501,7 @@
       <c r="AY34" s="3"/>
       <c r="AZ34" s="3"/>
     </row>
-    <row r="35" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -2771,7 +3553,7 @@
       <c r="AY35" s="3"/>
       <c r="AZ35" s="3"/>
     </row>
-    <row r="36" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2823,7 +3605,7 @@
       <c r="AY36" s="3"/>
       <c r="AZ36" s="3"/>
     </row>
-    <row r="37" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2875,7 +3657,7 @@
       <c r="AY37" s="3"/>
       <c r="AZ37" s="3"/>
     </row>
-    <row r="38" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2927,7 +3709,7 @@
       <c r="AY38" s="3"/>
       <c r="AZ38" s="3"/>
     </row>
-    <row r="39" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2979,7 +3761,7 @@
       <c r="AY39" s="3"/>
       <c r="AZ39" s="3"/>
     </row>
-    <row r="40" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3031,7 +3813,7 @@
       <c r="AY40" s="3"/>
       <c r="AZ40" s="3"/>
     </row>
-    <row r="41" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3083,7 +3865,7 @@
       <c r="AY41" s="3"/>
       <c r="AZ41" s="3"/>
     </row>
-    <row r="42" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -3135,7 +3917,7 @@
       <c r="AY42" s="3"/>
       <c r="AZ42" s="3"/>
     </row>
-    <row r="43" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -3187,7 +3969,7 @@
       <c r="AY43" s="3"/>
       <c r="AZ43" s="3"/>
     </row>
-    <row r="44" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -3239,7 +4021,7 @@
       <c r="AY44" s="3"/>
       <c r="AZ44" s="3"/>
     </row>
-    <row r="45" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -3291,7 +4073,7 @@
       <c r="AY45" s="3"/>
       <c r="AZ45" s="3"/>
     </row>
-    <row r="46" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3343,7 +4125,7 @@
       <c r="AY46" s="3"/>
       <c r="AZ46" s="3"/>
     </row>
-    <row r="47" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -3395,7 +4177,7 @@
       <c r="AY47" s="3"/>
       <c r="AZ47" s="3"/>
     </row>
-    <row r="48" spans="3:52" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:52" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -15719,6 +16501,110 @@
       <c r="AY284" s="3"/>
       <c r="AZ284" s="3"/>
     </row>
+    <row r="285" spans="3:52" x14ac:dyDescent="0.2">
+      <c r="C285" s="3"/>
+      <c r="D285" s="3"/>
+      <c r="E285" s="3"/>
+      <c r="F285" s="3"/>
+      <c r="G285" s="3"/>
+      <c r="H285" s="3"/>
+      <c r="I285" s="3"/>
+      <c r="J285" s="3"/>
+      <c r="K285" s="3"/>
+      <c r="L285" s="3"/>
+      <c r="M285" s="3"/>
+      <c r="N285" s="3"/>
+      <c r="O285" s="3"/>
+      <c r="P285" s="3"/>
+      <c r="Q285" s="3"/>
+      <c r="R285" s="3"/>
+      <c r="S285" s="3"/>
+      <c r="T285" s="3"/>
+      <c r="U285" s="3"/>
+      <c r="V285" s="3"/>
+      <c r="W285" s="3"/>
+      <c r="X285" s="3"/>
+      <c r="Y285" s="3"/>
+      <c r="Z285" s="3"/>
+      <c r="AA285" s="3"/>
+      <c r="AB285" s="3"/>
+      <c r="AC285" s="3"/>
+      <c r="AD285" s="3"/>
+      <c r="AE285" s="3"/>
+      <c r="AF285" s="3"/>
+      <c r="AG285" s="3"/>
+      <c r="AH285" s="3"/>
+      <c r="AI285" s="3"/>
+      <c r="AJ285" s="3"/>
+      <c r="AK285" s="3"/>
+      <c r="AL285" s="3"/>
+      <c r="AM285" s="3"/>
+      <c r="AN285" s="3"/>
+      <c r="AO285" s="3"/>
+      <c r="AP285" s="3"/>
+      <c r="AQ285" s="3"/>
+      <c r="AR285" s="3"/>
+      <c r="AS285" s="3"/>
+      <c r="AT285" s="3"/>
+      <c r="AU285" s="3"/>
+      <c r="AV285" s="3"/>
+      <c r="AW285" s="3"/>
+      <c r="AX285" s="3"/>
+      <c r="AY285" s="3"/>
+      <c r="AZ285" s="3"/>
+    </row>
+    <row r="286" spans="3:52" x14ac:dyDescent="0.2">
+      <c r="C286" s="3"/>
+      <c r="D286" s="3"/>
+      <c r="E286" s="3"/>
+      <c r="F286" s="3"/>
+      <c r="G286" s="3"/>
+      <c r="H286" s="3"/>
+      <c r="I286" s="3"/>
+      <c r="J286" s="3"/>
+      <c r="K286" s="3"/>
+      <c r="L286" s="3"/>
+      <c r="M286" s="3"/>
+      <c r="N286" s="3"/>
+      <c r="O286" s="3"/>
+      <c r="P286" s="3"/>
+      <c r="Q286" s="3"/>
+      <c r="R286" s="3"/>
+      <c r="S286" s="3"/>
+      <c r="T286" s="3"/>
+      <c r="U286" s="3"/>
+      <c r="V286" s="3"/>
+      <c r="W286" s="3"/>
+      <c r="X286" s="3"/>
+      <c r="Y286" s="3"/>
+      <c r="Z286" s="3"/>
+      <c r="AA286" s="3"/>
+      <c r="AB286" s="3"/>
+      <c r="AC286" s="3"/>
+      <c r="AD286" s="3"/>
+      <c r="AE286" s="3"/>
+      <c r="AF286" s="3"/>
+      <c r="AG286" s="3"/>
+      <c r="AH286" s="3"/>
+      <c r="AI286" s="3"/>
+      <c r="AJ286" s="3"/>
+      <c r="AK286" s="3"/>
+      <c r="AL286" s="3"/>
+      <c r="AM286" s="3"/>
+      <c r="AN286" s="3"/>
+      <c r="AO286" s="3"/>
+      <c r="AP286" s="3"/>
+      <c r="AQ286" s="3"/>
+      <c r="AR286" s="3"/>
+      <c r="AS286" s="3"/>
+      <c r="AT286" s="3"/>
+      <c r="AU286" s="3"/>
+      <c r="AV286" s="3"/>
+      <c r="AW286" s="3"/>
+      <c r="AX286" s="3"/>
+      <c r="AY286" s="3"/>
+      <c r="AZ286" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{20B2418A-132D-4A24-B91E-3081C97D8FA4}"/>
